--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66354941</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,8 +919,17 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85201252</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,846 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/85201252</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136439742</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110045</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sydväst om Sibbarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>428670</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6427862</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Främst i innerslänt men även i dikesbotten. Spritt längs en sträcka av ca 3 meter längs väg, ca 1,5 m på var sida av denna punkt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439742</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136439754</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110045</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Öster om Sandhem, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>428344</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6427933</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I slutet av och strax bortom bankslänt. Ytterligare två rapporteringar med andra plantor strax väster om denna punkt.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439754</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136439757</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110045</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öster om Sandhem, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>428315</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6427935</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I hela vägområdet, de flesta i innerslänt på norra sidan om vägen. Längs ca 15 m (punkten sitter i mitten). Fler i slänt strax österut, se egen rapportering.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439757</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136439740</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110308</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öster om Sandhem, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>428707</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6427846</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På södra sidan om vägen. Främst i dikesbotten, lite i ytterslänt. Längs ca fem meter.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439740</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136439752</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110308</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öster om Sandhem, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>428344</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6427934</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 10 tal plantor i innerslänt, utspritt på ca 1 sida av varje sida av punkt.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439752</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136439759</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110308</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skattegården södra, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>428293</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6427932</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Glest bestånd av svinrot på ca 1 meter på var sida av denna punkt längs väg. I innerslänt</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439759</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136439734</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102776</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öster om Sandhem, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>428697</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6427865</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Främst i ytterslänt på norra sidan om vägen. Längs ca åtta meter.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439734</t>
         </is>
       </c>
     </row>
@@ -929,6 +1769,13 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136439742</v>
       </c>
       <c r="B4" t="n">
-        <v>110045</v>
+        <v>110058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136439754</v>
       </c>
       <c r="B5" t="n">
-        <v>110045</v>
+        <v>110058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136439757</v>
       </c>
       <c r="B6" t="n">
-        <v>110045</v>
+        <v>110058</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>136439740</v>
       </c>
       <c r="B7" t="n">
-        <v>110308</v>
+        <v>110321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136439752</v>
       </c>
       <c r="B8" t="n">
-        <v>110308</v>
+        <v>110321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136439759</v>
       </c>
       <c r="B9" t="n">
-        <v>110308</v>
+        <v>110321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136439734</v>
       </c>
       <c r="B10" t="n">
-        <v>102776</v>
+        <v>102789</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7821-2024 artfynd.xlsx
+++ b/artfynd/A 7821-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>136439742</v>
       </c>
       <c r="B4" t="n">
-        <v>110058</v>
+        <v>110059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136439754</v>
       </c>
       <c r="B5" t="n">
-        <v>110058</v>
+        <v>110059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>136439757</v>
       </c>
       <c r="B6" t="n">
-        <v>110058</v>
+        <v>110059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>136439740</v>
       </c>
       <c r="B7" t="n">
-        <v>110321</v>
+        <v>110322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>136439752</v>
       </c>
       <c r="B8" t="n">
-        <v>110321</v>
+        <v>110322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>136439759</v>
       </c>
       <c r="B9" t="n">
-        <v>110321</v>
+        <v>110322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136439734</v>
       </c>
       <c r="B10" t="n">
-        <v>102789</v>
+        <v>102790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
